--- a/new original/_Dialog/Drama/_main.xlsx
+++ b/new original/_Dialog/Drama/_main.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1132" uniqueCount="489">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1134" uniqueCount="491">
   <si>
     <t xml:space="preserve">version</t>
   </si>
@@ -1191,6 +1191,12 @@
   </si>
   <si>
     <t xml:space="preserve">QuestExploration_AfterCrystal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">getAchievement</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ONEV</t>
   </si>
   <si>
     <t xml:space="preserve">bg_road</t>
@@ -15379,6 +15385,14 @@
         <v>106</v>
       </c>
     </row>
+    <row r="277" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D277" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="E277" s="1" t="s">
+        <v>322</v>
+      </c>
+    </row>
     <row r="282" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B282" s="1" t="s">
         <v>110</v>
@@ -15657,7 +15671,7 @@
         <v>128</v>
       </c>
       <c r="E288" s="1" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
     </row>
     <row r="289" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15937,10 +15951,10 @@
         <v>83</v>
       </c>
       <c r="I291" s="4" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="J291" s="4" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="K291" s="1"/>
       <c r="L291" s="1"/>
@@ -16198,10 +16212,10 @@
         <v>84</v>
       </c>
       <c r="I293" s="4" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="J293" s="4" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="K293" s="1"/>
       <c r="L293" s="1"/>
@@ -16473,10 +16487,10 @@
         <v>86</v>
       </c>
       <c r="I295" s="6" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="J295" s="6" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
     </row>
     <row r="296" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16487,10 +16501,10 @@
         <v>87</v>
       </c>
       <c r="I296" s="4" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="J296" s="4" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
     </row>
     <row r="297" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16501,10 +16515,10 @@
         <v>88</v>
       </c>
       <c r="I297" s="4" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="J297" s="4" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
     </row>
     <row r="298" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16515,10 +16529,10 @@
         <v>89</v>
       </c>
       <c r="I298" s="6" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="J298" s="6" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
     </row>
     <row r="299" customFormat="false" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16529,10 +16543,10 @@
         <v>90</v>
       </c>
       <c r="I299" s="6" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="J299" s="6" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
     </row>
     <row r="300" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16543,10 +16557,10 @@
         <v>91</v>
       </c>
       <c r="I300" s="4" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="J300" s="4" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
     </row>
     <row r="301" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16557,10 +16571,10 @@
         <v>92</v>
       </c>
       <c r="I301" s="6" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="J301" s="6" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
     </row>
     <row r="302" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16571,10 +16585,10 @@
         <v>93</v>
       </c>
       <c r="I302" s="4" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="J302" s="4" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="303" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16585,10 +16599,10 @@
         <v>94</v>
       </c>
       <c r="I303" s="6" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="J303" s="6" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
     </row>
     <row r="304" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16599,10 +16613,10 @@
         <v>95</v>
       </c>
       <c r="I304" s="4" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="J304" s="4" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
     </row>
     <row r="305" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16613,10 +16627,10 @@
         <v>96</v>
       </c>
       <c r="I305" s="4" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="J305" s="4" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
     </row>
     <row r="306" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16641,10 +16655,10 @@
         <v>98</v>
       </c>
       <c r="I307" s="4" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="J307" s="4" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
     </row>
     <row r="308" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16655,10 +16669,10 @@
         <v>99</v>
       </c>
       <c r="I308" s="4" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="J308" s="4" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
     </row>
     <row r="309" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16683,10 +16697,10 @@
         <v>101</v>
       </c>
       <c r="I310" s="6" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="J310" s="6" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
     </row>
     <row r="311" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16741,7 +16755,7 @@
         <v>86</v>
       </c>
       <c r="E321" s="1" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
     </row>
     <row r="322" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16764,7 +16778,7 @@
         <v>106</v>
       </c>
       <c r="I323" s="6" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="J323" s="4"/>
       <c r="K323" s="1"/>
@@ -17020,7 +17034,7 @@
         <v>107</v>
       </c>
       <c r="I324" s="6" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
     </row>
     <row r="325" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17028,7 +17042,7 @@
         <v>108</v>
       </c>
       <c r="I325" s="4" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="K325" s="1"/>
       <c r="L325" s="1"/>
@@ -17283,7 +17297,7 @@
         <v>109</v>
       </c>
       <c r="I326" s="4" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
     </row>
     <row r="327" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17291,7 +17305,7 @@
         <v>110</v>
       </c>
       <c r="I327" s="6" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
     </row>
     <row r="328" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17299,7 +17313,7 @@
         <v>111</v>
       </c>
       <c r="I328" s="4" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
     </row>
     <row r="329" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17307,7 +17321,7 @@
         <v>112</v>
       </c>
       <c r="I329" s="4" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
     </row>
     <row r="330" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17331,7 +17345,7 @@
         <v>128</v>
       </c>
       <c r="E334" s="1" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
     </row>
     <row r="335" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17339,7 +17353,7 @@
         <v>86</v>
       </c>
       <c r="E335" s="1" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
     </row>
     <row r="337" s="9" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17872,7 +17886,7 @@
         <v>113</v>
       </c>
       <c r="I339" s="6" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="K339" s="1"/>
       <c r="L339" s="1"/>
@@ -18130,7 +18144,7 @@
         <v>114</v>
       </c>
       <c r="I340" s="4" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="K340" s="1"/>
       <c r="L340" s="1"/>
@@ -18388,7 +18402,7 @@
         <v>115</v>
       </c>
       <c r="I341" s="4" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
     </row>
     <row r="342" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18399,7 +18413,7 @@
         <v>116</v>
       </c>
       <c r="I342" s="4" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
     </row>
     <row r="343" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18418,7 +18432,7 @@
         <v>117</v>
       </c>
       <c r="I344" s="4" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
     </row>
     <row r="345" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18429,7 +18443,7 @@
         <v>118</v>
       </c>
       <c r="I345" s="4" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
     </row>
     <row r="346" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18440,7 +18454,7 @@
         <v>119</v>
       </c>
       <c r="I346" s="4" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
     </row>
     <row r="347" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18451,7 +18465,7 @@
         <v>120</v>
       </c>
       <c r="I347" s="4" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
     </row>
     <row r="348" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18462,7 +18476,7 @@
         <v>121</v>
       </c>
       <c r="I348" s="4" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
     </row>
     <row r="349" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18470,7 +18484,7 @@
         <v>86</v>
       </c>
       <c r="E349" s="1" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
     </row>
     <row r="350" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18481,7 +18495,7 @@
         <v>122</v>
       </c>
       <c r="I350" s="4" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
     </row>
     <row r="351" s="9" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19003,7 +19017,7 @@
         <v>128</v>
       </c>
       <c r="E354" s="1" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
     </row>
     <row r="355" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19014,7 +19028,7 @@
         <v>86</v>
       </c>
       <c r="E355" s="1" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
     </row>
     <row r="356" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19292,7 +19306,7 @@
         <v>123</v>
       </c>
       <c r="I358" s="4" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
     </row>
     <row r="359" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19557,7 +19571,7 @@
         <v>128</v>
       </c>
       <c r="E361" s="1" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
     </row>
     <row r="362" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19568,7 +19582,7 @@
         <v>86</v>
       </c>
       <c r="E362" s="1" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
     </row>
     <row r="363" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19593,7 +19607,7 @@
         <v>124</v>
       </c>
       <c r="I364" s="4" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="J364" s="4"/>
       <c r="K364" s="1"/>
@@ -19852,7 +19866,7 @@
         <v>125</v>
       </c>
       <c r="I365" s="4" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
     </row>
     <row r="366" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19863,7 +19877,7 @@
         <v>126</v>
       </c>
       <c r="I366" s="4" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="K366" s="1"/>
       <c r="L366" s="1"/>
@@ -20121,7 +20135,7 @@
         <v>127</v>
       </c>
       <c r="I367" s="4" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
     </row>
     <row r="368" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20132,7 +20146,7 @@
         <v>128</v>
       </c>
       <c r="I368" s="6" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
     </row>
     <row r="369" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20143,7 +20157,7 @@
         <v>129</v>
       </c>
       <c r="I369" s="6" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
     </row>
     <row r="370" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20154,7 +20168,7 @@
         <v>130</v>
       </c>
       <c r="I370" s="6" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
     </row>
     <row r="371" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20165,7 +20179,7 @@
         <v>131</v>
       </c>
       <c r="I371" s="4" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
     </row>
     <row r="372" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20176,7 +20190,7 @@
         <v>132</v>
       </c>
       <c r="I372" s="4" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
     </row>
     <row r="373" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20187,7 +20201,7 @@
         <v>133</v>
       </c>
       <c r="I373" s="4" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
     </row>
     <row r="374" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20198,7 +20212,7 @@
         <v>134</v>
       </c>
       <c r="I374" s="4" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
     </row>
     <row r="375" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20209,7 +20223,7 @@
         <v>135</v>
       </c>
       <c r="I375" s="6" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
     </row>
     <row r="376" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20220,7 +20234,7 @@
         <v>136</v>
       </c>
       <c r="I376" s="4" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
     </row>
     <row r="377" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20231,7 +20245,7 @@
         <v>137</v>
       </c>
       <c r="I377" s="4" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
     </row>
     <row r="378" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20242,7 +20256,7 @@
         <v>138</v>
       </c>
       <c r="I378" s="4" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
     </row>
     <row r="379" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20258,7 +20272,7 @@
         <v>134</v>
       </c>
       <c r="E380" s="1" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
     </row>
     <row r="381" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20272,7 +20286,7 @@
         <v>139</v>
       </c>
       <c r="I381" s="6" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
     </row>
     <row r="382" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20315,7 +20329,7 @@
         <v>86</v>
       </c>
       <c r="E386" s="1" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
     </row>
     <row r="387" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20338,7 +20352,7 @@
         <v>140</v>
       </c>
       <c r="I388" s="4" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="J388" s="4"/>
       <c r="K388" s="1"/>
@@ -20594,7 +20608,7 @@
         <v>141</v>
       </c>
       <c r="I389" s="6" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
     </row>
     <row r="390" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20602,7 +20616,7 @@
         <v>142</v>
       </c>
       <c r="I390" s="4" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="K390" s="1"/>
       <c r="L390" s="1"/>
@@ -20857,7 +20871,7 @@
         <v>143</v>
       </c>
       <c r="I391" s="4" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
     </row>
     <row r="392" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20865,7 +20879,7 @@
         <v>144</v>
       </c>
       <c r="I392" s="4" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="394" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -21407,7 +21421,7 @@
         <v>128</v>
       </c>
       <c r="E402" s="1" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
     </row>
     <row r="403" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -21415,7 +21429,7 @@
         <v>86</v>
       </c>
       <c r="E403" s="1" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="405" s="9" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -21695,7 +21709,7 @@
         <v>145</v>
       </c>
       <c r="I406" s="4" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="J406" s="4"/>
       <c r="K406" s="1"/>
@@ -21954,7 +21968,7 @@
         <v>146</v>
       </c>
       <c r="I407" s="4" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="K407" s="1"/>
       <c r="L407" s="1"/>
@@ -22212,7 +22226,7 @@
         <v>147</v>
       </c>
       <c r="I408" s="4" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="K408" s="1"/>
       <c r="L408" s="1"/>
@@ -22470,7 +22484,7 @@
         <v>148</v>
       </c>
       <c r="I409" s="4" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
     </row>
     <row r="410" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -22481,7 +22495,7 @@
         <v>149</v>
       </c>
       <c r="I410" s="6" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
     </row>
     <row r="411" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -22492,7 +22506,7 @@
         <v>150</v>
       </c>
       <c r="I411" s="4" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
     </row>
     <row r="412" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -22503,7 +22517,7 @@
         <v>151</v>
       </c>
       <c r="I412" s="4" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
     </row>
     <row r="413" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -22514,7 +22528,7 @@
         <v>152</v>
       </c>
       <c r="I413" s="4" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
     </row>
     <row r="414" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -22525,7 +22539,7 @@
         <v>153</v>
       </c>
       <c r="I414" s="4" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
     </row>
     <row r="415" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -22533,7 +22547,7 @@
         <v>86</v>
       </c>
       <c r="E415" s="1" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
     </row>
     <row r="416" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23075,7 +23089,7 @@
         <v>154</v>
       </c>
       <c r="I420" s="4" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
     </row>
     <row r="421" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23083,7 +23097,7 @@
         <v>155</v>
       </c>
       <c r="I421" s="4" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
     </row>
     <row r="422" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23099,7 +23113,7 @@
         <v>128</v>
       </c>
       <c r="E423" s="1" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
     </row>
     <row r="424" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23123,7 +23137,7 @@
         <v>156</v>
       </c>
       <c r="I427" s="4" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
     </row>
     <row r="429" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23134,7 +23148,7 @@
         <v>157</v>
       </c>
       <c r="I429" s="4" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
     </row>
     <row r="430" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23145,7 +23159,7 @@
         <v>158</v>
       </c>
       <c r="I430" s="4" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
     </row>
     <row r="432" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23185,7 +23199,7 @@
         <v>159</v>
       </c>
       <c r="I436" s="6" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
     </row>
     <row r="437" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23201,7 +23215,7 @@
         <v>128</v>
       </c>
       <c r="E438" s="1" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
     </row>
     <row r="439" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23228,7 +23242,7 @@
         <v>160</v>
       </c>
       <c r="I442" s="6" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
     </row>
     <row r="443" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23239,7 +23253,7 @@
         <v>161</v>
       </c>
       <c r="I443" s="4" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
     </row>
     <row r="444" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23250,7 +23264,7 @@
         <v>162</v>
       </c>
       <c r="I444" s="4" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
     </row>
     <row r="446" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23290,7 +23304,7 @@
         <v>163</v>
       </c>
       <c r="I450" s="4" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
     </row>
     <row r="451" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23298,7 +23312,7 @@
         <v>164</v>
       </c>
       <c r="I451" s="6" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
     </row>
     <row r="452" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23306,7 +23320,7 @@
         <v>165</v>
       </c>
       <c r="I452" s="4" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
     </row>
     <row r="453" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23322,7 +23336,7 @@
         <v>166</v>
       </c>
       <c r="I454" s="4" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
     </row>
     <row r="456" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23330,7 +23344,7 @@
         <v>167</v>
       </c>
       <c r="I456" s="4" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
     </row>
     <row r="457" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23338,7 +23352,7 @@
         <v>168</v>
       </c>
       <c r="I457" s="4" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
     </row>
     <row r="460" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23346,7 +23360,7 @@
         <v>86</v>
       </c>
       <c r="E460" s="1" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
     </row>
     <row r="461" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23354,7 +23368,7 @@
         <v>169</v>
       </c>
       <c r="I461" s="4" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
     </row>
     <row r="462" s="9" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23625,7 +23639,7 @@
         <v>128</v>
       </c>
       <c r="E463" s="1" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
     </row>
     <row r="464" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23636,7 +23650,7 @@
         <v>86</v>
       </c>
       <c r="E464" s="1" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="K464" s="1"/>
       <c r="L464" s="1"/>
@@ -24671,7 +24685,7 @@
         <v>170</v>
       </c>
       <c r="I469" s="4" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="K469" s="1"/>
       <c r="L469" s="1"/>
@@ -24929,7 +24943,7 @@
         <v>171</v>
       </c>
       <c r="I470" s="6" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
     </row>
     <row r="471" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -24940,7 +24954,7 @@
         <v>172</v>
       </c>
       <c r="I471" s="4" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
     </row>
     <row r="472" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -24951,7 +24965,7 @@
         <v>173</v>
       </c>
       <c r="I472" s="4" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
     </row>
     <row r="473" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -24962,7 +24976,7 @@
         <v>174</v>
       </c>
       <c r="I473" s="4" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
     </row>
     <row r="474" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -24973,7 +24987,7 @@
         <v>175</v>
       </c>
       <c r="I474" s="4" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
     </row>
     <row r="476" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -24981,7 +24995,7 @@
         <v>102</v>
       </c>
       <c r="E476" s="1" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
     </row>
     <row r="477" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -24989,7 +25003,7 @@
         <v>128</v>
       </c>
       <c r="E477" s="1" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
     </row>
     <row r="478" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -24997,7 +25011,7 @@
         <v>86</v>
       </c>
       <c r="E478" s="1" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="480" s="9" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -25277,7 +25291,7 @@
         <v>176</v>
       </c>
       <c r="I481" s="4" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="J481" s="4"/>
       <c r="K481" s="1"/>
@@ -25536,7 +25550,7 @@
         <v>177</v>
       </c>
       <c r="I482" s="4" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="K482" s="1"/>
       <c r="L482" s="1"/>
@@ -26638,7 +26652,7 @@
         <v>61</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26646,7 +26660,7 @@
         <v>61</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26654,12 +26668,12 @@
         <v>61</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D9" s="1" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26701,7 +26715,7 @@
         <v>86</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="K18" s="1"/>
       <c r="L18" s="1"/>
@@ -27218,10 +27232,10 @@
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I21" s="1" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="J21" s="1" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -27477,15 +27491,15 @@
         <v>128</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I25" s="1" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="J25" s="1" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -27538,7 +27552,7 @@
         <v>86</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="K36" s="1"/>
       <c r="L36" s="1"/>
@@ -28055,10 +28069,10 @@
     </row>
     <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I39" s="1" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="J39" s="1" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -28348,7 +28362,7 @@
         <v>86</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="K51" s="1"/>
       <c r="L51" s="1"/>
@@ -29112,10 +29126,10 @@
         <v>1</v>
       </c>
       <c r="I54" s="1" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="J54" s="1" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29377,10 +29391,10 @@
         <v>2</v>
       </c>
       <c r="I56" s="10" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="J56" s="10" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29388,10 +29402,10 @@
         <v>3</v>
       </c>
       <c r="I57" s="10" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="J57" s="10" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29407,10 +29421,10 @@
         <v>4</v>
       </c>
       <c r="I59" s="10" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="J59" s="10" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29418,10 +29432,10 @@
         <v>5</v>
       </c>
       <c r="I60" s="10" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="J60" s="10" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29429,10 +29443,10 @@
         <v>6</v>
       </c>
       <c r="I61" s="10" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="J61" s="10" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29448,10 +29462,10 @@
         <v>7</v>
       </c>
       <c r="I63" s="10" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="J63" s="10" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29459,10 +29473,10 @@
         <v>8</v>
       </c>
       <c r="I64" s="10" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="J64" s="10" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29470,10 +29484,10 @@
         <v>9</v>
       </c>
       <c r="I65" s="10" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="J65" s="10" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29481,10 +29495,10 @@
         <v>10</v>
       </c>
       <c r="I66" s="10" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="J66" s="10" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29531,7 +29545,7 @@
         <v>86</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="K79" s="1"/>
       <c r="L79" s="1"/>
@@ -30295,10 +30309,10 @@
         <v>31</v>
       </c>
       <c r="I82" s="1" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="J82" s="1" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -30560,10 +30574,10 @@
         <v>32</v>
       </c>
       <c r="I84" s="1" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="J84" s="1" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -30616,7 +30630,7 @@
         <v>86</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="K96" s="1"/>
       <c r="L96" s="1"/>
@@ -30878,7 +30892,7 @@
         <v>11</v>
       </c>
       <c r="I99" s="10" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -30886,7 +30900,7 @@
         <v>12</v>
       </c>
       <c r="I100" s="10" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -30894,7 +30908,7 @@
         <v>13</v>
       </c>
       <c r="I101" s="10" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -30910,7 +30924,7 @@
         <v>14</v>
       </c>
       <c r="I103" s="10" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -30918,7 +30932,7 @@
         <v>15</v>
       </c>
       <c r="I104" s="10" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
     </row>
     <row r="105" s="9" customFormat="true" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -30933,7 +30947,7 @@
         <v>16</v>
       </c>
       <c r="I105" s="10" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="J105" s="1"/>
       <c r="K105" s="1"/>
@@ -31188,7 +31202,7 @@
         <v>17</v>
       </c>
       <c r="I106" s="10" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="K106" s="1"/>
       <c r="L106" s="1"/>
@@ -31450,7 +31464,7 @@
         <v>18</v>
       </c>
       <c r="I108" s="10" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="K108" s="1"/>
       <c r="L108" s="1"/>
@@ -31712,7 +31726,7 @@
         <v>19</v>
       </c>
       <c r="I110" s="1" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
     </row>
     <row r="111" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31720,7 +31734,7 @@
         <v>20</v>
       </c>
       <c r="I111" s="10" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31728,7 +31742,7 @@
         <v>21</v>
       </c>
       <c r="I112" s="10" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
     </row>
     <row r="113" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31736,7 +31750,7 @@
         <v>22</v>
       </c>
       <c r="I113" s="10" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
     </row>
     <row r="114" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31744,7 +31758,7 @@
         <v>23</v>
       </c>
       <c r="I114" s="10" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
     </row>
     <row r="115" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31752,7 +31766,7 @@
         <v>24</v>
       </c>
       <c r="I115" s="10" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="L115" s="1"/>
     </row>
@@ -31761,7 +31775,7 @@
         <v>25</v>
       </c>
       <c r="I116" s="1" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="117" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31777,7 +31791,7 @@
         <v>26</v>
       </c>
       <c r="I118" s="10" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
     </row>
     <row r="119" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31785,7 +31799,7 @@
         <v>27</v>
       </c>
       <c r="I119" s="10" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
     </row>
     <row r="120" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31793,7 +31807,7 @@
         <v>28</v>
       </c>
       <c r="I120" s="10" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
     </row>
     <row r="121" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31801,7 +31815,7 @@
         <v>29</v>
       </c>
       <c r="I121" s="10" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
     </row>
     <row r="122" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31809,7 +31823,7 @@
         <v>30</v>
       </c>
       <c r="I122" s="10" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
     </row>
     <row r="123" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31841,7 +31855,7 @@
         <v>86</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="K126" s="1"/>
       <c r="L126" s="1"/>
@@ -32100,7 +32114,7 @@
     </row>
     <row r="128" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D128" s="1" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
     </row>
     <row r="129" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32896,7 +32910,7 @@
         <v>86</v>
       </c>
       <c r="E141" s="1" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="K141" s="1"/>
       <c r="L141" s="1"/>
@@ -33155,7 +33169,7 @@
     </row>
     <row r="143" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D143" s="1" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
     </row>
     <row r="144" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
